--- a/Normalisasi_SalesDB_Irza.xlsx
+++ b/Normalisasi_SalesDB_Irza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fariz Irza\Documents\Magang\Gawe\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C62E4D7-8D76-4031-BE3F-0C9C6FC80E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE4A5E6-C5A5-42B3-B4BC-47135CEE4526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="131">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -489,10 +489,31 @@
 </t>
   </si>
   <si>
-    <t>Kolom A, Kolom C, Kolom G, Kolom I</t>
-  </si>
-  <si>
     <t>Saya merubah kolom yang tadinya terdapat lebih dari satu value menjadi satu, karena terdapat repeating group pada beberapa kolom dari no fakturnya.</t>
+  </si>
+  <si>
+    <t>A -&gt; B, C, D || G -&gt; H</t>
+  </si>
+  <si>
+    <t>Kolom A, Kolom G</t>
+  </si>
+  <si>
+    <t>Tabel Faktur</t>
+  </si>
+  <si>
+    <t>Tabel Produk</t>
+  </si>
+  <si>
+    <t>Tabel Invoice</t>
+  </si>
+  <si>
+    <t>No Faktur, dan Kode Produk termasuk PK FK juga karena termasuk candidate key</t>
+  </si>
+  <si>
+    <t>saya memisahkan tabelnya dan menambahkan 1 tabel transaksi, yaitu tabel invoice</t>
+  </si>
+  <si>
+    <t>No Faktur -&gt; Tanggal, Kode Pelanggan, Nama Pelanggan, Email, Kota || Kode Produk -&gt; Nama Produk, Kode Kategori, Nama Kategori . || (No Faktur, Kode Produk) -&gt; Qty (Full)</t>
   </si>
 </sst>
 </file>
@@ -500,9 +521,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,8 +599,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -611,6 +640,12 @@
         <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -639,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -657,7 +692,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -667,7 +702,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -682,6 +717,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1119,7 +1159,7 @@
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
@@ -1512,7 +1552,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
@@ -1522,7 +1562,9 @@
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>123</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
@@ -1532,7 +1574,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1540,14 +1582,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="11" t="s">
@@ -1565,7 +1607,7 @@
       <c r="H11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="11" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="11" t="s">
@@ -1581,14 +1623,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="13">
         <v>46266</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="12" t="s">
@@ -1600,13 +1642,13 @@
       <c r="F12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="24" t="s">
         <v>107</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="12" t="s">
         <v>64</v>
       </c>
       <c r="J12" s="12" t="s">
@@ -1623,13 +1665,13 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46266</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="12" t="s">
@@ -1641,13 +1683,13 @@
       <c r="F13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="24" t="s">
         <v>108</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="12" t="s">
         <v>111</v>
       </c>
       <c r="J13" s="12" t="s">
@@ -1664,13 +1706,13 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="13">
         <v>46275</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="12" t="s">
@@ -1682,13 +1724,13 @@
       <c r="F14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>114</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="12" t="s">
         <v>111</v>
       </c>
       <c r="J14" s="12" t="s">
@@ -1705,13 +1747,13 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="13">
         <v>46275</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="12" t="s">
@@ -1723,13 +1765,13 @@
       <c r="F15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="24" t="s">
         <v>108</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="12" t="s">
         <v>111</v>
       </c>
       <c r="J15" s="12" t="s">
@@ -1746,13 +1788,13 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="24" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="13">
         <v>46277</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="12" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="12" t="s">
@@ -1764,13 +1806,13 @@
       <c r="F16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="24" t="s">
         <v>62</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="12" t="s">
         <v>64</v>
       </c>
       <c r="J16" s="12" t="s">
@@ -1787,13 +1829,13 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="24" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="13">
         <v>46280</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1805,13 +1847,13 @@
       <c r="F17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="24" t="s">
         <v>120</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="12" t="s">
         <v>117</v>
       </c>
       <c r="J17" s="12" t="s">
@@ -1828,13 +1870,13 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="24" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="13">
         <v>46280</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="12" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="12" t="s">
@@ -1846,13 +1888,13 @@
       <c r="F18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="24" t="s">
         <v>115</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="12" t="s">
         <v>117</v>
       </c>
       <c r="J18" s="12" t="s">
@@ -1869,13 +1911,13 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B19" s="13">
         <v>46283</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="12" t="s">
@@ -1887,13 +1929,13 @@
       <c r="F19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="24" t="s">
         <v>62</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="22" t="s">
+      <c r="I19" s="12" t="s">
         <v>64</v>
       </c>
       <c r="J19" s="12" t="s">
@@ -1910,13 +1952,13 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="13">
         <v>46283</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="12" t="s">
@@ -1928,13 +1970,13 @@
       <c r="F20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="24" t="s">
         <v>120</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="12" t="s">
         <v>121</v>
       </c>
       <c r="J20" s="12" t="s">
@@ -1951,13 +1993,13 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="13">
         <v>46283</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="12" t="s">
@@ -1969,13 +2011,13 @@
       <c r="F21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="24" t="s">
         <v>115</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="I21" s="12" t="s">
         <v>117</v>
       </c>
       <c r="J21" s="12" t="s">
@@ -1992,13 +2034,13 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="24" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="13">
         <v>46285</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="12" t="s">
         <v>58</v>
       </c>
       <c r="D22" s="12" t="s">
@@ -2010,13 +2052,13 @@
       <c r="F22" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="24" t="s">
         <v>107</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="I22" s="12" t="s">
         <v>64</v>
       </c>
       <c r="J22" s="12" t="s">
@@ -2033,13 +2075,13 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="24" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="13">
         <v>46285</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="12" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="12" t="s">
@@ -2051,13 +2093,13 @@
       <c r="F23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="24" t="s">
         <v>114</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="12" t="s">
         <v>111</v>
       </c>
       <c r="J23" s="12" t="s">
@@ -2081,65 +2123,490 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="72.5546875" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
+    <col min="11" max="11" width="7.77734375" customWidth="1"/>
+    <col min="12" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="14">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="14">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="14">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="14">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="12">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Normalisasi_SalesDB_Irza.xlsx
+++ b/Normalisasi_SalesDB_Irza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fariz Irza\Documents\Magang\Gawe\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE4A5E6-C5A5-42B3-B4BC-47135CEE4526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49C5A4-5877-47A5-87CE-9565D0082425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -85,8 +85,56 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{1751782E-BA27-4A09-967E-696BB85C9CF9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{CE614FAC-E9E6-427C-A9FE-51DA32BC456E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="142">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -514,6 +562,39 @@
   </si>
   <si>
     <t>No Faktur -&gt; Tanggal, Kode Pelanggan, Nama Pelanggan, Email, Kota || Kode Produk -&gt; Nama Produk, Kode Kategori, Nama Kategori . || (No Faktur, Kode Produk) -&gt; Qty (Full)</t>
+  </si>
+  <si>
+    <t>Tabel Kategori</t>
+  </si>
+  <si>
+    <t>Tabel Pelanggan</t>
+  </si>
+  <si>
+    <t>No Faktur (PK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur (PK, FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK, FK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur, Kode Produk, Kode Kategori, Kode Pelanggan</t>
+  </si>
+  <si>
+    <t>Saya mengubah primary keynya menjadi 4 supaya tidak ada lagi transitive dependency, dengan total tabel yaitu 5</t>
+  </si>
+  <si>
+    <t>Menjadi Full semua tabel</t>
   </si>
 </sst>
 </file>
@@ -632,17 +713,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,7 +765,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -699,9 +780,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -714,20 +794,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF8CBAD"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1137,13 +1228,13 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1172,7 +1263,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1182,322 +1273,322 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <v>46266</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>2150000</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>46275</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
         <v>900000</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
         <v>46277</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="13">
         <v>1050000</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <v>46280</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="13">
         <v>346000</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>46283</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="13">
         <v>548000</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>46285</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="13">
         <v>4450000</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="18" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="18" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="18" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1528,7 +1619,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1548,32 +1639,32 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="21" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1583,535 +1674,535 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>46266</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="11">
         <v>1</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="13">
         <v>1850000</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="13">
         <v>2150000</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>46266</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>2</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="13">
         <v>150000</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="13">
         <v>2150000</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <v>46275</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>1</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="13">
         <v>750000</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="13">
         <v>900000</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>46275</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>1</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="13">
         <v>150000</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="13">
         <v>900000</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <v>46277</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>3</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="13">
         <v>350000</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="13">
         <v>1050000</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <v>46280</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <v>10</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="13">
         <v>25000</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="13">
         <v>346000</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <v>46280</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <v>2</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="13">
         <v>48000</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="13">
         <v>346000</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="12">
         <v>46283</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <v>1</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="13">
         <v>375000</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="13">
         <v>548000</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>46283</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <v>5</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="13">
         <v>25000</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="13">
         <v>548000</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="12">
         <v>46283</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <v>1</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="13">
         <v>48000</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="13">
         <v>548000</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="12">
         <v>46285</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="11">
         <v>2</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="13">
         <v>1850000</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="13">
         <v>4450000</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="12">
         <v>46285</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="11">
         <v>1</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="13">
         <v>750000</v>
       </c>
-      <c r="M23" s="14">
+      <c r="M23" s="13">
         <v>4450000</v>
       </c>
     </row>
@@ -2122,8 +2213,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2132,7 +2223,7 @@
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="19.6640625" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" customWidth="1"/>
     <col min="10" max="10" width="13.77734375" customWidth="1"/>
@@ -2140,491 +2231,532 @@
     <col min="12" max="13" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="13">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="12">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="13">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="13">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="13">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="12">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="13">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="12">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="13">
+        <v>4450000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="B32" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13">
-        <v>46266</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="B33" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="11">
+        <v>2</v>
+      </c>
+      <c r="D34" s="13">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="13">
-        <v>46275</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+      <c r="B35" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="13">
-        <v>46277</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="B37" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="11">
+        <v>3</v>
+      </c>
+      <c r="D37" s="13">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="13">
-        <v>46280</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="B38" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="11">
+        <v>10</v>
+      </c>
+      <c r="D38" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="11">
+        <v>2</v>
+      </c>
+      <c r="D39" s="13">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="13">
-        <v>46283</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="B40" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="11">
+        <v>5</v>
+      </c>
+      <c r="D41" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="11">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="13">
-        <v>46285</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="B43" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="14">
+      <c r="C43" s="11">
+        <v>2</v>
+      </c>
+      <c r="D43" s="13">
         <v>1850000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="14">
-        <v>350000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="14">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="14">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="14">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="C44" s="11">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13">
         <v>750000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C43" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="12">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2644,28 +2776,34 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="15" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -2673,9 +2811,435 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
+      <c r="A11" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="13">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="12">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="13">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="13">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="12">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="13">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="12">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="13">
+        <v>4450000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="11">
+        <v>2</v>
+      </c>
+      <c r="D34" s="13">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="11">
+        <v>3</v>
+      </c>
+      <c r="D37" s="13">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="11">
+        <v>10</v>
+      </c>
+      <c r="D38" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="11">
+        <v>2</v>
+      </c>
+      <c r="D39" s="13">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="11">
+        <v>5</v>
+      </c>
+      <c r="D41" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="11">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="11">
+        <v>2</v>
+      </c>
+      <c r="D43" s="13">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="11">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Normalisasi_SalesDB_Irza.xlsx
+++ b/Normalisasi_SalesDB_Irza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fariz Irza\Documents\Magang\Gawe\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49C5A4-5877-47A5-87CE-9565D0082425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D782C0EF-0490-40E3-9909-3B239F74FC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="5_ERD" sheetId="6" r:id="rId6"/>
+    <sheet name="6_QuerySQL" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -115,7 +117,7 @@
     <author>Trainer</author>
   </authors>
   <commentList>
-    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{CE614FAC-E9E6-427C-A9FE-51DA32BC456E}">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{CE614FAC-E9E6-427C-A9FE-51DA32BC456E}">
       <text>
         <r>
           <rPr>
@@ -134,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="146">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -595,6 +597,120 @@
   </si>
   <si>
     <t>Menjadi Full semua tabel</t>
+  </si>
+  <si>
+    <t>Kode Kategori (FK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (FK)</t>
+  </si>
+  <si>
+    <t>Tabel Detail_Faktur</t>
+  </si>
+  <si>
+    <t>IF DB_ID(N'SalesDB') IS NULL
+	CREATE DATABASE SalesDB;
+GO
+USE SalesDB
+GO
+CREATE TABLE Costumer (
+CostumerID UNIQUEIDENTIFIER NOT NULL,
+Costumer_Name NVARCHAR(50) NOT NULL,
+Email NVARCHAR(50) NOT NULL,
+City NVARCHAR(50) NOT NULL,
+CONSTRAINT PK_Costumer PRIMARY KEY (CostumerID)
+)
+GO
+CREATE UNIQUE NONCLUSTERED INDEX UQ_Costumer_Email
+	ON dbo.Costumer (Email)
+	WHERE Email IS NOT NULL;
+GO
+CREATE TABLE Category (
+CategoryID INT IDENTITY(1,1) NOT NULL,
+SubCategoryID INT NULL,
+Category_Name NVARCHAR(50) NOT NULL,
+CONSTRAINT PK_Category PRIMARY KEY (CategoryID),
+CONSTRAINT FK_Category_SubCategory FOREIGN KEY (SubCategoryID) REFERENCES Category(CategoryID)
+)
+GO
+CREATE TABLE [Order] (
+OrderID UNIQUEIDENTIFIER NOT NULL,
+CostumerID UNIQUEIDENTIFIER NOT NULL,
+Date DATETIME2 NOT NULL CONSTRAINT DF_Order_Date DEFAULT GETDATE(),
+CONSTRAINT PK_Order PRIMARY KEY (OrderID),
+CONSTRAINT FK_Order_Costumer FOREIGN KEY (CostumerID) REFERENCES Costumer(CostumerID)
+)
+GO
+CREATE TABLE Product (
+ProductID INT IDENTITY(1,1) NOT NULL,
+CategoryID INT NOT NULL,
+Product_Name NVARCHAR(50) NOT NULL,
+Unit_Price DECIMAL(12,2) NOT NULL,
+Stock INT NOT NULL,
+CONSTRAINT PK_Product PRIMARY KEY (ProductID),
+CONSTRAINT FK_Product_Category FOREIGN KEY (CategoryID) REFERENCES Category(CategoryID)
+)
+GO
+CREATE TABLE Order_Detail (
+OrderID UNIQUEIDENTIFIER NOT NULL,
+ProductID INT NOT NULL,
+Quantity INT NOT NULL,
+Unit_Price DECIMAL(12,2) NOT NULL,
+CONSTRAINT PK_Order_Detail PRIMARY KEY (OrderID, ProductID),
+CONSTRAINT FK_Order_Detail_Order FOREIGN KEY (OrderID) REFERENCES [Order](OrderID),
+CONSTRAINT FK_Order_Detail_Product FOREIGN KEY (ProductID) REFERENCES Product(ProductID),
+CONSTRAINT CK_Quantity CHECK (Quantity&gt;0)
+)
+GO
+DECLARE @C1 UNIQUEIDENTIFIER = NEWID();
+DECLARE @C2 UNIQUEIDENTIFIER = NEWID();
+DECLARE @C3 UNIQUEIDENTIFIER = NEWID();
+INSERT INTO dbo.Costumer (CostumerID, Costumer_Name, Email, City)
+VALUES	(@C1, N'Budi Santoso', N'budi@mail.com', 'Jakarta'),
+		(@C2, N'Siti Aminah', N'siti@mail.com', 'Bandung'),
+		(@C3, N'Andi Wijaya', N'andi@mail.com', 'Surabaya');
+INSERT INTO dbo.Category (SubCategoryID, Category_Name)
+VALUES	(NULL, N'Elektronik'),
+		(NULL, N'Alat Tulis'),
+		(NULL, N'Aksesoris Komputer');
+INSERT INTO dbo.Product (CategoryID,	Product_Name, Unit_Price, Stock)
+VALUES	(1, N'Monitor 24 inci', 1850000, 5),
+		(3, N'Headset USB', 350000, 10),
+		(2, N'Buku Catatan A5', 25000, 15),
+		(2, N'Pulpen Gel (isi 12)', 48000, 20),
+		(3, N'Mouse Wireless', 150000, 25),
+		(3, N'Keyboard Mekanik', 750000, 30);
+DECLARE @O1 UNIQUEIDENTIFIER = NEWID();
+DECLARE @O2 UNIQUEIDENTIFIER = NEWID();
+DECLARE @O3 UNIQUEIDENTIFIER = NEWID();
+DECLARE @O4 UNIQUEIDENTIFIER = NEWID();
+DECLARE @O5 UNIQUEIDENTIFIER = NEWID();
+DECLARE @O6 UNIQUEIDENTIFIER = NEWID();
+INSERT INTO dbo.[Order] (OrderID, CostumerID, Date)
+VALUES	(@O1, @C1, '2026-09-01'),
+		(@O2, @C2, '2026-09-10'),
+		(@O3, @C3, '2026-09-12'),
+		(@O4, @C1, '2026-09-15'),
+		(@O5, @C2, '2026-09-18'),
+		(@O6, @C3, '2026-09-20');
+INSERT INTO dbo.Order_Detail (OrderID, ProductID, Quantity, Unit_Price)
+VALUES	(@O1, 1, 1, 1850000),
+		(@O1, 5, 2, 150000),
+		(@O2, 6, 1, 750000),
+		(@O2, 5, 1, 150000),
+		(@O3, 2, 3, 350000),
+		(@O4, 3, 10, 25000),
+		(@O4, 4, 2, 48000),
+		(@O5, 2, 1, 350000),
+		(@O5, 3, 5, 25000),
+		(@O5, 4, 1, 48000),
+		(@O6, 1, 2, 1850000),
+		(@O6, 6, 1, 750000);
+SELECT * FROM Costumer
+SELECT * FROM Category
+SELECT * FROM Product
+SELECT * FROM [Order]
+SELECT * FROM Order_Detail</t>
   </si>
 </sst>
 </file>
@@ -604,7 +720,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -688,6 +804,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -708,11 +836,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
@@ -725,6 +848,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CBAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -764,7 +893,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -780,7 +908,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -794,19 +922,29 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -816,6 +954,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC6E0B4"/>
       <color rgb="FFF8CBAD"/>
     </mruColors>
   </colors>
@@ -828,6 +967,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>585305</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>94796</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96C828B4-347D-D60F-2297-2128C5DAFC25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12777305" cy="6571796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1222,19 +1410,19 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1263,7 +1451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1273,322 +1461,322 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>46266</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <v>2150000</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>46275</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <v>900000</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>46277</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="12">
         <v>1050000</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>46280</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <v>346000</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>46283</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <v>548000</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>46285</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="12">
         <v>4450000</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="17" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="17" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1619,7 +1807,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1639,32 +1827,32 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1674,535 +1862,535 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>46266</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>1</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="12">
         <v>1850000</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="12">
         <v>2150000</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>46266</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <v>2</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="12">
         <v>150000</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <v>2150000</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>46275</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <v>1</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="12">
         <v>750000</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="12">
         <v>900000</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>46275</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="10">
         <v>1</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="12">
         <v>150000</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="12">
         <v>900000</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>46277</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <v>3</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="12">
         <v>350000</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="12">
         <v>1050000</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>46280</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <v>10</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="12">
         <v>25000</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="12">
         <v>346000</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>46280</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="10">
         <v>2</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="12">
         <v>48000</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <v>346000</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>46283</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="10">
         <v>1</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="12">
         <v>375000</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="12">
         <v>548000</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>46283</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <v>5</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="12">
         <v>25000</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="12">
         <v>548000</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>46283</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="10">
         <v>1</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="12">
         <v>48000</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="12">
         <v>548000</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>46285</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="10">
         <v>2</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="12">
         <v>1850000</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="12">
         <v>4450000</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>46285</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="J23" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="10">
         <v>1</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="12">
         <v>750000</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="12">
         <v>4450000</v>
       </c>
     </row>
@@ -2232,7 +2420,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2252,28 +2440,28 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="15"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2288,453 +2476,453 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>46266</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>2150000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>46275</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <v>900000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>46277</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>1050000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>46280</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>346000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>46283</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>548000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>46285</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>4450000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>1</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <v>1850000</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>2</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="12">
         <v>150000</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>1</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <v>750000</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>1</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <v>150000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>3</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <v>350000</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>10</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <v>25000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>2</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <v>48000</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>1</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="12">
         <v>350000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>5</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="12">
         <v>25000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>1</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="12">
         <v>48000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>2</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>1850000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>1</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="12">
         <v>750000</v>
       </c>
     </row>
@@ -2752,489 +2940,531 @@
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>46266</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="12">
         <v>2150000</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>46275</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="12">
         <v>900000</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>46277</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12">
         <v>1050000</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>46280</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="12">
         <v>346000</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>46283</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12">
         <v>548000</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>46285</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="12">
         <v>4450000</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>29</v>
       </c>
+      <c r="C22" s="18" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>109</v>
       </c>
+      <c r="C23" s="27" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>63</v>
       </c>
+      <c r="C24" s="27" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>119</v>
       </c>
+      <c r="C25" s="27" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>116</v>
       </c>
+      <c r="C26" s="27" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="C27" s="27" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>113</v>
       </c>
+      <c r="C28" s="27" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
-        <v>127</v>
+      <c r="A31" s="22" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>1</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <v>1850000</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="10">
         <v>2</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="12">
         <v>150000</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>1</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <v>750000</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="10">
         <v>1</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <v>150000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>3</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <v>350000</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>10</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <v>25000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>2</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <v>48000</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="10">
         <v>1</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="12">
         <v>350000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>5</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="12">
         <v>25000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="10">
         <v>1</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="12">
         <v>48000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>2</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>1850000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>1</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="12">
         <v>750000</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="25" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="22" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="19" t="s">
+      <c r="A55" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="10" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3242,4 +3472,387 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789E4B3C-B193-45E4-A791-FA15540AE0B3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53738DD1-9626-4D9D-9745-E58F6C13D459}">
+  <dimension ref="A1:A118"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="95.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="29"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="29"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="29"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="29"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="29"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="29"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="29"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="29"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="29"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="29"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="29"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="29"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="29"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="29"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="29"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="29"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="29"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="29"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="29"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="29"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="29"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="29"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="29"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="29"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="29"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="29"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="29"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="29"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="29"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="29"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="29"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="29"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="29"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="29"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="29"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="29"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="29"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="29"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="29"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="29"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="29"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="29"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="29"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="29"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="29"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="29"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="29"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="29"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="29"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="29"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="29"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="29"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="29"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="29"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="29"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="29"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="29"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="29"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="29"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="29"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="29"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="29"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="29"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="29"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="29"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="29"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="29"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="29"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="29"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="29"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="29"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="29"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="29"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="29"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="29"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="29"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="29"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="29"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="29"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="29"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="29"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="29"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="29"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="29"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="29"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="29"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="29"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="29"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="29"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="29"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="29"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="29"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="29"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="29"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="29"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="29"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="29"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="29"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="29"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="29"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="29"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="29"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="29"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="29"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="29"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="29"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A118"/>
+  </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Normalisasi_SalesDB_Irza.xlsx
+++ b/Normalisasi_SalesDB_Irza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fariz Irza\Documents\Magang\Gawe\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D782C0EF-0490-40E3-9909-3B239F74FC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3C8227-C583-4A5C-B018-C8CFC6AD4480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,20 @@
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
     <sheet name="5_ERD" sheetId="6" r:id="rId6"/>
     <sheet name="6_QuerySQL" sheetId="7" r:id="rId7"/>
+    <sheet name="7_Latihan QuerySQL 1 &amp; 2" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -136,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="198">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -712,6 +724,2739 @@
 SELECT * FROM [Order]
 SELECT * FROM Order_Detail</t>
   </si>
+  <si>
+    <t>-- Latihan 1</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Costumer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> @C4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Costumer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CostumerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Costumer_Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>@C4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Dewi Lestari'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Jakarta'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Unit_Price </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'375000'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>OUTPUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  deleted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Unit_Price </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OldPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Unit_price </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NewPrice</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>OUTPUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  deleted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OldStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NewStock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 200</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 20 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+  </si>
+  <si>
+    <t>--Latihan 2</t>
+  </si>
+  <si>
+    <r>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> @ValidOrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TOP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1 OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Order_Detail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Unit_Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>@ValidOrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Msg 547, Level 16, State 0, Line 195</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CostumerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>GETDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>())</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Msg 206, Level 16, State 2, Line 199</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Product_Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Unit_Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Iphone 18 Pro Max Burgundy'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 29999000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Msg 547, Level 16, State 0, Line 203</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> @C5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>@C5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Irza Alfarizi'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Bekasi'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Berhasil</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Costumer</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> @C6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>@C6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'M Irza Alfarizi'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'budi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Bekasi'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Msg 2601, Level 14, State 1, Line 215</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TRAN</t>
+    </r>
+  </si>
+  <si>
+    <t>ROLLBACK</t>
+  </si>
+  <si>
+    <t>COMMIT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                                      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--The INSERT statement conflicted with the CHECK constraint "CK_Quantity". The conflict occurred in database "SalesDB", table "dbo.Order_Detail", column 'Quantity'.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Operand type clash: int is incompatible with uniqueidentifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                                                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--The INSERT statement conflicted with the CHECK constraint "CK_Stock_NonNegative". The conflict occurred in database "SalesDB", table "dbo.Product", column 'Stock'.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                                                             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--Cannot insert duplicate key row in object 'dbo.Costumer' with unique index 'UQ_Costumer_Email'. The duplicate key value is (budi@mail.com).</t>
+    </r>
+  </si>
+  <si>
+    <t>Penjelasan Aturan/Constraint Bisnis yang dijaga:</t>
+  </si>
+  <si>
+    <t>1. Terdapat constraint check yang melihat apakah kuantitas dari order itu lebih dari 0 atau tidak, jika = 0 maka Query akan ditolak</t>
+  </si>
+  <si>
+    <t>2. Untuk CostumerID 99 itu tidak bisa karena ID dari costumer sudah auto generate dari GUID</t>
+  </si>
+  <si>
+    <t>3. Produk dengan Stok 5 tidak bisa diterima karena ada constraint yang melihat apakah produk yang ditambahkan itu stoknya ada atau tidak (&gt;=0), bukan minus</t>
+  </si>
+  <si>
+    <t>4. Pelanggan baru tanpa email/NULL itu masih bisa diterima karena aturan bisnisnya tidak mewajibkan email harus ada pada sebuah akun</t>
+  </si>
+  <si>
+    <t>5. Pelanggan baru dengan email budi@mail.com akan ditolak, karena email itu sebelumnya sudah ada di costumer Budi Santoso</t>
+  </si>
 </sst>
 </file>
 
@@ -720,7 +3465,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -816,6 +3561,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF008000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -885,7 +3660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,6 +3720,21 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3188,7 +5978,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>135</v>
       </c>
@@ -3855,4 +6645,348 @@
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217281F5-2938-4D0F-8D7D-1D0F886FD82A}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="66.88671875" customWidth="1"/>
+    <col min="2" max="2" width="167" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="30"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="30"/>
+      <c r="B7" s="30"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" s="32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="30"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" s="32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="30"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="30"/>
+      <c r="B21" s="32" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="30"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="30"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="30"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="30"/>
+      <c r="B39" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="32" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="30"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>